--- a/branches/Richard/ValueSet-vs-vl-suppression.xlsx
+++ b/branches/Richard/ValueSet-vs-vl-suppression.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-28T11:18:10+00:00</t>
+    <t>2023-04-28T11:24:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/ValueSet-vs-vl-suppression.xlsx
+++ b/branches/Richard/ValueSet-vs-vl-suppression.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-28T11:24:11+00:00</t>
+    <t>2023-04-28T11:24:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/ValueSet-vs-vl-suppression.xlsx
+++ b/branches/Richard/ValueSet-vs-vl-suppression.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-28T11:24:31+00:00</t>
+    <t>2023-04-30T03:44:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/ValueSet-vs-vl-suppression.xlsx
+++ b/branches/Richard/ValueSet-vs-vl-suppression.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-30T03:44:40+00:00</t>
+    <t>2023-04-30T03:44:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/ValueSet-vs-vl-suppression.xlsx
+++ b/branches/Richard/ValueSet-vs-vl-suppression.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-30T03:44:58+00:00</t>
+    <t>2023-04-30T03:52:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/ValueSet-vs-vl-suppression.xlsx
+++ b/branches/Richard/ValueSet-vs-vl-suppression.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-30T03:52:18+00:00</t>
+    <t>2023-04-30T03:53:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/ValueSet-vs-vl-suppression.xlsx
+++ b/branches/Richard/ValueSet-vs-vl-suppression.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-30T03:53:51+00:00</t>
+    <t>2023-04-30T09:28:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/ValueSet-vs-vl-suppression.xlsx
+++ b/branches/Richard/ValueSet-vs-vl-suppression.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-30T09:28:44+00:00</t>
+    <t>2023-05-01T08:52:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/ValueSet-vs-vl-suppression.xlsx
+++ b/branches/Richard/ValueSet-vs-vl-suppression.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-01T08:52:03+00:00</t>
+    <t>2023-05-01T08:56:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/ValueSet-vs-vl-suppression.xlsx
+++ b/branches/Richard/ValueSet-vs-vl-suppression.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-01T08:56:42+00:00</t>
+    <t>2023-05-01T09:10:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/ValueSet-vs-vl-suppression.xlsx
+++ b/branches/Richard/ValueSet-vs-vl-suppression.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-01T09:10:15+00:00</t>
+    <t>2023-05-01T09:11:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/ValueSet-vs-vl-suppression.xlsx
+++ b/branches/Richard/ValueSet-vs-vl-suppression.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-01T09:11:26+00:00</t>
+    <t>2023-05-01T09:13:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/ValueSet-vs-vl-suppression.xlsx
+++ b/branches/Richard/ValueSet-vs-vl-suppression.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-01T09:13:53+00:00</t>
+    <t>2023-05-01T09:16:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/ValueSet-vs-vl-suppression.xlsx
+++ b/branches/Richard/ValueSet-vs-vl-suppression.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-01T09:16:45+00:00</t>
+    <t>2023-05-01T16:40:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/ValueSet-vs-vl-suppression.xlsx
+++ b/branches/Richard/ValueSet-vs-vl-suppression.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-01T16:40:06+00:00</t>
+    <t>2023-05-01T16:40:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/ValueSet-vs-vl-suppression.xlsx
+++ b/branches/Richard/ValueSet-vs-vl-suppression.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-01T16:40:27+00:00</t>
+    <t>2023-05-01T18:12:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/ValueSet-vs-vl-suppression.xlsx
+++ b/branches/Richard/ValueSet-vs-vl-suppression.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-01T18:12:00+00:00</t>
+    <t>2023-05-01T18:12:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/ValueSet-vs-vl-suppression.xlsx
+++ b/branches/Richard/ValueSet-vs-vl-suppression.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-01T18:12:07+00:00</t>
+    <t>2023-05-02T21:23:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/ValueSet-vs-vl-suppression.xlsx
+++ b/branches/Richard/ValueSet-vs-vl-suppression.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T21:23:22+00:00</t>
+    <t>2023-05-02T21:27:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/ValueSet-vs-vl-suppression.xlsx
+++ b/branches/Richard/ValueSet-vs-vl-suppression.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T21:27:47+00:00</t>
+    <t>2023-05-03T08:35:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/ValueSet-vs-vl-suppression.xlsx
+++ b/branches/Richard/ValueSet-vs-vl-suppression.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-03T08:35:52+00:00</t>
+    <t>2023-05-03T08:46:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/ValueSet-vs-vl-suppression.xlsx
+++ b/branches/Richard/ValueSet-vs-vl-suppression.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-03T08:46:45+00:00</t>
+    <t>2023-05-03T08:57:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/ValueSet-vs-vl-suppression.xlsx
+++ b/branches/Richard/ValueSet-vs-vl-suppression.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-03T08:57:04+00:00</t>
+    <t>2023-05-03T08:57:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/ValueSet-vs-vl-suppression.xlsx
+++ b/branches/Richard/ValueSet-vs-vl-suppression.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-03T08:57:52+00:00</t>
+    <t>2023-05-04T12:38:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/ValueSet-vs-vl-suppression.xlsx
+++ b/branches/Richard/ValueSet-vs-vl-suppression.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-04T12:38:34+00:00</t>
+    <t>2023-05-04T12:42:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/ValueSet-vs-vl-suppression.xlsx
+++ b/branches/Richard/ValueSet-vs-vl-suppression.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-04T12:42:53+00:00</t>
+    <t>2023-05-05T21:01:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/ValueSet-vs-vl-suppression.xlsx
+++ b/branches/Richard/ValueSet-vs-vl-suppression.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T21:01:51+00:00</t>
+    <t>2023-05-06T12:10:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/ValueSet-vs-vl-suppression.xlsx
+++ b/branches/Richard/ValueSet-vs-vl-suppression.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-06T12:10:27+00:00</t>
+    <t>2023-05-06T12:11:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/ValueSet-vs-vl-suppression.xlsx
+++ b/branches/Richard/ValueSet-vs-vl-suppression.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-06T12:11:33+00:00</t>
+    <t>2023-05-07T12:05:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/ValueSet-vs-vl-suppression.xlsx
+++ b/branches/Richard/ValueSet-vs-vl-suppression.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T12:05:50+00:00</t>
+    <t>2023-05-07T12:06:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/ValueSet-vs-vl-suppression.xlsx
+++ b/branches/Richard/ValueSet-vs-vl-suppression.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T12:06:01+00:00</t>
+    <t>2023-05-07T12:57:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/ValueSet-vs-vl-suppression.xlsx
+++ b/branches/Richard/ValueSet-vs-vl-suppression.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T12:57:45+00:00</t>
+    <t>2023-05-07T12:58:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/ValueSet-vs-vl-suppression.xlsx
+++ b/branches/Richard/ValueSet-vs-vl-suppression.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T12:58:10+00:00</t>
+    <t>2023-05-07T13:06:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/ValueSet-vs-vl-suppression.xlsx
+++ b/branches/Richard/ValueSet-vs-vl-suppression.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T13:06:46+00:00</t>
+    <t>2023-05-07T13:07:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/ValueSet-vs-vl-suppression.xlsx
+++ b/branches/Richard/ValueSet-vs-vl-suppression.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T13:07:20+00:00</t>
+    <t>2023-05-07T13:57:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/ValueSet-vs-vl-suppression.xlsx
+++ b/branches/Richard/ValueSet-vs-vl-suppression.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T13:57:21+00:00</t>
+    <t>2023-05-08T06:55:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/ValueSet-vs-vl-suppression.xlsx
+++ b/branches/Richard/ValueSet-vs-vl-suppression.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T06:55:13+00:00</t>
+    <t>2023-05-08T06:55:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/ValueSet-vs-vl-suppression.xlsx
+++ b/branches/Richard/ValueSet-vs-vl-suppression.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T06:55:26+00:00</t>
+    <t>2023-05-08T13:44:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/ValueSet-vs-vl-suppression.xlsx
+++ b/branches/Richard/ValueSet-vs-vl-suppression.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T13:44:54+00:00</t>
+    <t>2023-05-08T13:51:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/ValueSet-vs-vl-suppression.xlsx
+++ b/branches/Richard/ValueSet-vs-vl-suppression.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T13:51:23+00:00</t>
+    <t>2023-05-08T14:05:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/ValueSet-vs-vl-suppression.xlsx
+++ b/branches/Richard/ValueSet-vs-vl-suppression.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T14:05:33+00:00</t>
+    <t>2023-05-08T14:07:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/ValueSet-vs-vl-suppression.xlsx
+++ b/branches/Richard/ValueSet-vs-vl-suppression.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T14:07:06+00:00</t>
+    <t>2023-05-08T14:23:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/ValueSet-vs-vl-suppression.xlsx
+++ b/branches/Richard/ValueSet-vs-vl-suppression.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T14:23:05+00:00</t>
+    <t>2023-05-08T14:48:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/ValueSet-vs-vl-suppression.xlsx
+++ b/branches/Richard/ValueSet-vs-vl-suppression.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T14:48:00+00:00</t>
+    <t>2023-05-08T15:19:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/ValueSet-vs-vl-suppression.xlsx
+++ b/branches/Richard/ValueSet-vs-vl-suppression.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T15:19:54+00:00</t>
+    <t>2023-05-08T15:31:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/ValueSet-vs-vl-suppression.xlsx
+++ b/branches/Richard/ValueSet-vs-vl-suppression.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T15:31:47+00:00</t>
+    <t>2023-05-08T16:10:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/ValueSet-vs-vl-suppression.xlsx
+++ b/branches/Richard/ValueSet-vs-vl-suppression.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T16:10:55+00:00</t>
+    <t>2023-05-08T18:38:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/ValueSet-vs-vl-suppression.xlsx
+++ b/branches/Richard/ValueSet-vs-vl-suppression.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T18:38:59+00:00</t>
+    <t>2023-05-08T18:49:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/ValueSet-vs-vl-suppression.xlsx
+++ b/branches/Richard/ValueSet-vs-vl-suppression.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T18:49:00+00:00</t>
+    <t>2023-05-08T19:06:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/ValueSet-vs-vl-suppression.xlsx
+++ b/branches/Richard/ValueSet-vs-vl-suppression.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:06:08+00:00</t>
+    <t>2023-05-08T19:17:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/ValueSet-vs-vl-suppression.xlsx
+++ b/branches/Richard/ValueSet-vs-vl-suppression.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:17:16+00:00</t>
+    <t>2023-05-08T19:36:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/ValueSet-vs-vl-suppression.xlsx
+++ b/branches/Richard/ValueSet-vs-vl-suppression.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:36:32+00:00</t>
+    <t>2023-05-08T19:37:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/ValueSet-vs-vl-suppression.xlsx
+++ b/branches/Richard/ValueSet-vs-vl-suppression.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:37:24+00:00</t>
+    <t>2023-05-08T19:39:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/ValueSet-vs-vl-suppression.xlsx
+++ b/branches/Richard/ValueSet-vs-vl-suppression.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:39:41+00:00</t>
+    <t>2023-05-08T19:40:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/ValueSet-vs-vl-suppression.xlsx
+++ b/branches/Richard/ValueSet-vs-vl-suppression.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:40:43+00:00</t>
+    <t>2023-05-08T19:42:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/ValueSet-vs-vl-suppression.xlsx
+++ b/branches/Richard/ValueSet-vs-vl-suppression.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:42:22+00:00</t>
+    <t>2023-05-08T19:53:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/ValueSet-vs-vl-suppression.xlsx
+++ b/branches/Richard/ValueSet-vs-vl-suppression.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:53:59+00:00</t>
+    <t>2023-05-08T21:00:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/ValueSet-vs-vl-suppression.xlsx
+++ b/branches/Richard/ValueSet-vs-vl-suppression.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T21:00:30+00:00</t>
+    <t>2023-05-08T21:01:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/ValueSet-vs-vl-suppression.xlsx
+++ b/branches/Richard/ValueSet-vs-vl-suppression.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T21:01:17+00:00</t>
+    <t>2023-05-09T15:00:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/ValueSet-vs-vl-suppression.xlsx
+++ b/branches/Richard/ValueSet-vs-vl-suppression.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-09T15:00:51+00:00</t>
+    <t>2023-05-09T15:03:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/ValueSet-vs-vl-suppression.xlsx
+++ b/branches/Richard/ValueSet-vs-vl-suppression.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-09T15:03:02+00:00</t>
+    <t>2023-05-09T15:34:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/ValueSet-vs-vl-suppression.xlsx
+++ b/branches/Richard/ValueSet-vs-vl-suppression.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-09T15:34:42+00:00</t>
+    <t>2023-05-09T15:35:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
